--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsB2cDeclareReconciliationDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsB2cDeclareReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,13 +106,13 @@
     <t>{.actualBillingWeight}</t>
   </si>
   <si>
-    <t>{.actualShippingCost}</t>
-  </si>
-  <si>
-    <t>{.actualDeclareCost}</t>
-  </si>
-  <si>
-    <t>{.actualOtherCost}</t>
+    <t>{.actualShippingCostStr}</t>
+  </si>
+  <si>
+    <t>{.actualDeclareCostStr}</t>
+  </si>
+  <si>
+    <t>{.actualOtherCostStr}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1062,7 +1062,7 @@
     <col min="8" max="8" width="16.375" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="17.125" customWidth="1"/>
+    <col min="11" max="11" width="17.75" customWidth="1"/>
     <col min="12" max="12" width="16.375" customWidth="1"/>
     <col min="13" max="13" width="16.625" customWidth="1"/>
     <col min="14" max="14" width="12.875" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsB2cDeclareReconciliationDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsB2cDeclareReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>实际物流运费(总)</t>
   </si>
   <si>
-    <t>实际报关费用(总)</t>
+    <t>实际关税费用(总)</t>
   </si>
   <si>
     <t>实际其他费用(总)</t>
